--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ75"/>
+  <dimension ref="A1:AZ83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,56 +680,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123656502</v>
+        <v>136801971</v>
       </c>
       <c r="B2" t="n">
-        <v>57950</v>
+        <v>93408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1435</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Dlr</t>
+          <t>BJURTJÄRN, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513623</v>
+        <v>513643</v>
       </c>
       <c r="R2" t="n">
-        <v>6733240</v>
+        <v>6733226</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,27 +748,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Den hela svampen finns kvar som kollekt och torkas. Den är visad för kunniga på svampexkursion.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,6 +777,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,16 +795,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123656502</t>
+          <t>https://artportalen.se/Sighting/136801971</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123656503</v>
+        <v>136801973</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>96563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,45 +812,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Dlr</t>
+          <t>BJURTJÄRN, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513619</v>
+        <v>513660</v>
       </c>
       <c r="R3" t="n">
-        <v>6733230</v>
+        <v>6733221</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,27 +866,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,13 +907,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123656503</t>
+          <t>https://artportalen.se/Sighting/136801973</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123656504</v>
+        <v>123656502</v>
       </c>
       <c r="B4" t="n">
         <v>57950</v>
@@ -973,7 +956,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513643</v>
+        <v>513623</v>
       </c>
       <c r="R4" t="n">
         <v>6733240</v>
@@ -1008,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,12 +1001,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,13 +1032,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123656504</t>
+          <t>https://artportalen.se/Sighting/123656502</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123656505</v>
+        <v>123656503</v>
       </c>
       <c r="B5" t="n">
         <v>57950</v>
@@ -1098,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513624</v>
+        <v>513619</v>
       </c>
       <c r="R5" t="n">
-        <v>6733235</v>
+        <v>6733230</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1133,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1143,12 +1126,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,16 +1157,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123656505</t>
+          <t>https://artportalen.se/Sighting/123656503</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123253272</v>
+        <v>123656504</v>
       </c>
       <c r="B6" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,42 +1174,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Bjurtjärnsån, Dlr</t>
+          <t>Bjurtjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513623</v>
+        <v>513643</v>
       </c>
       <c r="R6" t="n">
-        <v>6733230</v>
+        <v>6733240</v>
       </c>
       <c r="S6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1250,22 +1236,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,27 +1271,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123253272</t>
+          <t>https://artportalen.se/Sighting/123656504</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123656500</v>
+        <v>123656505</v>
       </c>
       <c r="B7" t="n">
-        <v>5179</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,28 +1299,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1337,13 +1331,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513668</v>
+        <v>513624</v>
       </c>
       <c r="R7" t="n">
-        <v>6733244</v>
+        <v>6733235</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1367,22 +1361,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,7 +1390,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1403,22 +1401,22 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123656500</t>
+          <t>https://artportalen.se/Sighting/123656505</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123650523</v>
+        <v>136801962</v>
       </c>
       <c r="B8" t="n">
-        <v>57132</v>
+        <v>58005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,16 +1424,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1445,11 +1443,7 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1458,17 +1452,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Dlr</t>
+          <t>BJURTJÄRN, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513585</v>
+        <v>513540</v>
       </c>
       <c r="R8" t="n">
-        <v>6733249</v>
+        <v>6733263</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1492,27 +1486,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
+          <t>I en tall på en myr.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1538,16 +1532,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123650523</t>
+          <t>https://artportalen.se/Sighting/136801962</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123650524</v>
+        <v>136801970</v>
       </c>
       <c r="B9" t="n">
-        <v>57132</v>
+        <v>58005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,16 +1549,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1574,11 +1568,7 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1587,17 +1577,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Dlr</t>
+          <t>BJURTJÄRN, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513595</v>
+        <v>513625</v>
       </c>
       <c r="R9" t="n">
-        <v>6733257</v>
+        <v>6733229</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1621,22 +1611,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska spår av födosök på kullen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1662,16 +1657,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123650524</t>
+          <t>https://artportalen.se/Sighting/136801970</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123650526</v>
+        <v>123253272</v>
       </c>
       <c r="B10" t="n">
-        <v>57132</v>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,45 +1674,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Dlr</t>
+          <t>Bjurtjärnsån, Bjurtjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513627</v>
+        <v>513623</v>
       </c>
       <c r="R10" t="n">
-        <v>6733250</v>
+        <v>6733230</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1741,27 +1733,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:22</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1776,27 +1763,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123650526</t>
+          <t>https://artportalen.se/Sighting/123253272</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123650527</v>
+        <v>123656500</v>
       </c>
       <c r="B11" t="n">
-        <v>57132</v>
+        <v>5179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,31 +1791,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1836,13 +1820,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513634</v>
+        <v>513668</v>
       </c>
       <c r="R11" t="n">
-        <v>6733215</v>
+        <v>6733244</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1866,17 +1850,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>16:07</t>
+          <t>2001-01-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1885,6 +1874,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1896,22 +1886,22 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123650527</t>
+          <t>https://artportalen.se/Sighting/123656500</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123650528</v>
+        <v>136801976</v>
       </c>
       <c r="B12" t="n">
-        <v>57132</v>
+        <v>5182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,45 +1909,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Dlr</t>
+          <t>BJURTJÄRN, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513632</v>
+        <v>513667</v>
       </c>
       <c r="R12" t="n">
-        <v>6733214</v>
+        <v>6733237</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1981,22 +1963,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,69 +1998,72 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123650528</t>
+          <t>https://artportalen.se/Sighting/136801976</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123252664</v>
+        <v>123650523</v>
       </c>
       <c r="B13" t="n">
-        <v>99118</v>
+        <v>57132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Bjurtjärnsån, Dlr</t>
+          <t>Bjurtjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513616</v>
+        <v>513585</v>
       </c>
       <c r="R13" t="n">
         <v>6733249</v>
       </c>
       <c r="S13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2102,22 +2087,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2132,74 +2122,77 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123252664</t>
+          <t>https://artportalen.se/Sighting/123650523</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123252821</v>
+        <v>123650524</v>
       </c>
       <c r="B14" t="n">
-        <v>99118</v>
+        <v>57132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Bjurtjärnsån, Dlr</t>
+          <t>Bjurtjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513598</v>
+        <v>513595</v>
       </c>
       <c r="R14" t="n">
-        <v>6733234</v>
+        <v>6733257</v>
       </c>
       <c r="S14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2223,22 +2216,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2253,74 +2246,73 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123252821</t>
+          <t>https://artportalen.se/Sighting/123650524</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123253165</v>
+        <v>123650526</v>
       </c>
       <c r="B15" t="n">
-        <v>99118</v>
+        <v>57132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Bjurtjärnsån, Dlr</t>
+          <t>Bjurtjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513623</v>
+        <v>513627</v>
       </c>
       <c r="R15" t="n">
-        <v>6733230</v>
+        <v>6733250</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2344,22 +2336,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2374,55 +2371,59 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123253165</t>
+          <t>https://artportalen.se/Sighting/123650526</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123652160</v>
+        <v>123650527</v>
       </c>
       <c r="B16" t="n">
-        <v>99118</v>
+        <v>57132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2430,10 +2431,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513608</v>
+        <v>513634</v>
       </c>
       <c r="R16" t="n">
-        <v>6733246</v>
+        <v>6733215</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2463,24 +2464,14 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2489,7 +2480,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2507,44 +2497,48 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652160</t>
+          <t>https://artportalen.se/Sighting/123650527</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123652161</v>
+        <v>123650528</v>
       </c>
       <c r="B17" t="n">
-        <v>99118</v>
+        <v>57132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2552,10 +2546,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513597</v>
+        <v>513632</v>
       </c>
       <c r="R17" t="n">
-        <v>6733265</v>
+        <v>6733214</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2587,7 +2581,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2597,12 +2591,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2611,7 +2600,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2629,58 +2617,54 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652161</t>
+          <t>https://artportalen.se/Sighting/123650528</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123652162</v>
+        <v>136801972</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>8463</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Dlr</t>
+          <t>BJURTJÄRN, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513604</v>
+        <v>513642</v>
       </c>
       <c r="R18" t="n">
-        <v>6733250</v>
+        <v>6733221</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2704,27 +2688,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2733,7 +2712,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2751,58 +2729,54 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652162</t>
+          <t>https://artportalen.se/Sighting/136801972</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123652163</v>
+        <v>136801969</v>
       </c>
       <c r="B19" t="n">
-        <v>99118</v>
+        <v>111330</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Dlr</t>
+          <t>BJURTJÄRN, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513621</v>
+        <v>513592</v>
       </c>
       <c r="R19" t="n">
-        <v>6733235</v>
+        <v>6733244</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2826,27 +2800,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:52</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2855,7 +2824,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2873,13 +2841,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652163</t>
+          <t>https://artportalen.se/Sighting/136801969</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123652164</v>
+        <v>123252664</v>
       </c>
       <c r="B20" t="n">
         <v>99118</v>
@@ -2907,24 +2875,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Dlr</t>
+          <t>Bjurtjärnsån, Bjurtjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513617</v>
+        <v>513616</v>
       </c>
       <c r="R20" t="n">
-        <v>6733240</v>
+        <v>6733249</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2948,27 +2921,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2977,31 +2945,30 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652164</t>
+          <t>https://artportalen.se/Sighting/123252664</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123652168</v>
+        <v>123252821</v>
       </c>
       <c r="B21" t="n">
         <v>99118</v>
@@ -3029,24 +2996,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Dlr</t>
+          <t>Bjurtjärnsån, Bjurtjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513593</v>
+        <v>513598</v>
       </c>
       <c r="R21" t="n">
-        <v>6733228</v>
+        <v>6733234</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3070,27 +3042,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:26</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3099,31 +3066,30 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652168</t>
+          <t>https://artportalen.se/Sighting/123252821</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123652169</v>
+        <v>123253165</v>
       </c>
       <c r="B22" t="n">
         <v>99118</v>
@@ -3151,24 +3117,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Dlr</t>
+          <t>Bjurtjärnsån, Bjurtjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513603</v>
+        <v>513623</v>
       </c>
       <c r="R22" t="n">
-        <v>6733229</v>
+        <v>6733230</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3192,27 +3163,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3221,31 +3187,30 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652169</t>
+          <t>https://artportalen.se/Sighting/123253165</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123652170</v>
+        <v>123652160</v>
       </c>
       <c r="B23" t="n">
         <v>99118</v>
@@ -3284,10 +3249,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513607</v>
+        <v>513608</v>
       </c>
       <c r="R23" t="n">
-        <v>6733239</v>
+        <v>6733246</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3319,7 +3284,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3329,7 +3294,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3361,13 +3326,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652170</t>
+          <t>https://artportalen.se/Sighting/123652160</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123652171</v>
+        <v>123652161</v>
       </c>
       <c r="B24" t="n">
         <v>99118</v>
@@ -3406,10 +3371,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>513608</v>
+        <v>513597</v>
       </c>
       <c r="R24" t="n">
-        <v>6733238</v>
+        <v>6733265</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3441,7 +3406,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3451,12 +3416,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3477,19 +3442,19 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652171</t>
+          <t>https://artportalen.se/Sighting/123652161</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123652173</v>
+        <v>123652162</v>
       </c>
       <c r="B25" t="n">
         <v>99118</v>
@@ -3528,10 +3493,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>513600</v>
+        <v>513604</v>
       </c>
       <c r="R25" t="n">
-        <v>6733258</v>
+        <v>6733250</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3563,7 +3528,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3573,7 +3538,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3605,13 +3570,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652173</t>
+          <t>https://artportalen.se/Sighting/123652162</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123652174</v>
+        <v>123652163</v>
       </c>
       <c r="B26" t="n">
         <v>99118</v>
@@ -3650,13 +3615,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513606</v>
+        <v>513621</v>
       </c>
       <c r="R26" t="n">
-        <v>6733257</v>
+        <v>6733235</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3685,7 +3650,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3695,7 +3660,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3727,13 +3692,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652174</t>
+          <t>https://artportalen.se/Sighting/123652163</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123652175</v>
+        <v>123652164</v>
       </c>
       <c r="B27" t="n">
         <v>99118</v>
@@ -3772,10 +3737,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513606</v>
+        <v>513617</v>
       </c>
       <c r="R27" t="n">
-        <v>6733254</v>
+        <v>6733240</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3807,7 +3772,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3817,7 +3782,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3849,13 +3814,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652175</t>
+          <t>https://artportalen.se/Sighting/123652164</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123652176</v>
+        <v>123652168</v>
       </c>
       <c r="B28" t="n">
         <v>99118</v>
@@ -3894,10 +3859,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513605</v>
+        <v>513593</v>
       </c>
       <c r="R28" t="n">
-        <v>6733249</v>
+        <v>6733228</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3929,7 +3894,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3939,7 +3904,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3971,13 +3936,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652176</t>
+          <t>https://artportalen.se/Sighting/123652168</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123652177</v>
+        <v>123652169</v>
       </c>
       <c r="B29" t="n">
         <v>99118</v>
@@ -4016,10 +3981,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513615</v>
+        <v>513603</v>
       </c>
       <c r="R29" t="n">
-        <v>6733245</v>
+        <v>6733229</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4051,7 +4016,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4061,7 +4026,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4093,13 +4058,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652177</t>
+          <t>https://artportalen.se/Sighting/123652169</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123652178</v>
+        <v>123652170</v>
       </c>
       <c r="B30" t="n">
         <v>99118</v>
@@ -4138,10 +4103,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513605</v>
+        <v>513607</v>
       </c>
       <c r="R30" t="n">
-        <v>6733242</v>
+        <v>6733239</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4173,7 +4138,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4183,7 +4148,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4215,13 +4180,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652178</t>
+          <t>https://artportalen.se/Sighting/123652170</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123652179</v>
+        <v>123652171</v>
       </c>
       <c r="B31" t="n">
         <v>99118</v>
@@ -4260,10 +4225,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513611</v>
+        <v>513608</v>
       </c>
       <c r="R31" t="n">
-        <v>6733236</v>
+        <v>6733238</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4295,7 +4260,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4305,12 +4270,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4337,13 +4302,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652179</t>
+          <t>https://artportalen.se/Sighting/123652171</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123652180</v>
+        <v>123652173</v>
       </c>
       <c r="B32" t="n">
         <v>99118</v>
@@ -4382,10 +4347,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513623</v>
+        <v>513600</v>
       </c>
       <c r="R32" t="n">
-        <v>6733239</v>
+        <v>6733258</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4417,7 +4382,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4427,7 +4392,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4459,13 +4424,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652180</t>
+          <t>https://artportalen.se/Sighting/123652173</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123652181</v>
+        <v>123652174</v>
       </c>
       <c r="B33" t="n">
         <v>99118</v>
@@ -4504,10 +4469,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513619</v>
+        <v>513606</v>
       </c>
       <c r="R33" t="n">
-        <v>6733234</v>
+        <v>6733257</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4539,7 +4504,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4549,7 +4514,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4581,13 +4546,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652181</t>
+          <t>https://artportalen.se/Sighting/123652174</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123652182</v>
+        <v>123652175</v>
       </c>
       <c r="B34" t="n">
         <v>99118</v>
@@ -4626,10 +4591,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513620</v>
+        <v>513606</v>
       </c>
       <c r="R34" t="n">
-        <v>6733241</v>
+        <v>6733254</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4661,7 +4626,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4671,7 +4636,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4703,13 +4668,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652182</t>
+          <t>https://artportalen.se/Sighting/123652175</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123652184</v>
+        <v>123652176</v>
       </c>
       <c r="B35" t="n">
         <v>99118</v>
@@ -4748,10 +4713,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513618</v>
+        <v>513605</v>
       </c>
       <c r="R35" t="n">
-        <v>6733235</v>
+        <v>6733249</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4783,7 +4748,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4793,7 +4758,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4825,13 +4790,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652184</t>
+          <t>https://artportalen.se/Sighting/123652176</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123652185</v>
+        <v>123652177</v>
       </c>
       <c r="B36" t="n">
         <v>99118</v>
@@ -4870,10 +4835,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513619</v>
+        <v>513615</v>
       </c>
       <c r="R36" t="n">
-        <v>6733240</v>
+        <v>6733245</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4905,7 +4870,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4915,7 +4880,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4947,13 +4912,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652185</t>
+          <t>https://artportalen.se/Sighting/123652177</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123652186</v>
+        <v>123652178</v>
       </c>
       <c r="B37" t="n">
         <v>99118</v>
@@ -4992,10 +4957,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513623</v>
+        <v>513605</v>
       </c>
       <c r="R37" t="n">
-        <v>6733238</v>
+        <v>6733242</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5027,7 +4992,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5037,7 +5002,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5069,13 +5034,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652186</t>
+          <t>https://artportalen.se/Sighting/123652178</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123652187</v>
+        <v>123652179</v>
       </c>
       <c r="B38" t="n">
         <v>99118</v>
@@ -5114,10 +5079,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513627</v>
+        <v>513611</v>
       </c>
       <c r="R38" t="n">
-        <v>6733241</v>
+        <v>6733236</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5149,7 +5114,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5159,12 +5124,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5191,13 +5156,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652187</t>
+          <t>https://artportalen.se/Sighting/123652179</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123652188</v>
+        <v>123652180</v>
       </c>
       <c r="B39" t="n">
         <v>99118</v>
@@ -5236,7 +5201,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513629</v>
+        <v>513623</v>
       </c>
       <c r="R39" t="n">
         <v>6733239</v>
@@ -5271,7 +5236,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5281,7 +5246,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5313,13 +5278,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652188</t>
+          <t>https://artportalen.se/Sighting/123652180</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123652189</v>
+        <v>123652181</v>
       </c>
       <c r="B40" t="n">
         <v>99118</v>
@@ -5358,10 +5323,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513629</v>
+        <v>513619</v>
       </c>
       <c r="R40" t="n">
-        <v>6733228</v>
+        <v>6733234</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5393,7 +5358,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5403,12 +5368,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5435,13 +5400,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652189</t>
+          <t>https://artportalen.se/Sighting/123652181</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123652190</v>
+        <v>123652182</v>
       </c>
       <c r="B41" t="n">
         <v>99118</v>
@@ -5480,10 +5445,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513627</v>
+        <v>513620</v>
       </c>
       <c r="R41" t="n">
-        <v>6733227</v>
+        <v>6733241</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5515,7 +5480,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5525,7 +5490,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5557,13 +5522,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652190</t>
+          <t>https://artportalen.se/Sighting/123652182</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123652191</v>
+        <v>123652184</v>
       </c>
       <c r="B42" t="n">
         <v>99118</v>
@@ -5602,10 +5567,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513628</v>
+        <v>513618</v>
       </c>
       <c r="R42" t="n">
-        <v>6733228</v>
+        <v>6733235</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5637,7 +5602,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5647,7 +5612,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5679,13 +5644,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652191</t>
+          <t>https://artportalen.se/Sighting/123652184</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123652192</v>
+        <v>123652185</v>
       </c>
       <c r="B43" t="n">
         <v>99118</v>
@@ -5724,10 +5689,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513630</v>
+        <v>513619</v>
       </c>
       <c r="R43" t="n">
-        <v>6733221</v>
+        <v>6733240</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5759,7 +5724,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5769,7 +5734,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5801,13 +5766,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652192</t>
+          <t>https://artportalen.se/Sighting/123652185</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123652193</v>
+        <v>123652186</v>
       </c>
       <c r="B44" t="n">
         <v>99118</v>
@@ -5846,10 +5811,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513631</v>
+        <v>513623</v>
       </c>
       <c r="R44" t="n">
-        <v>6733221</v>
+        <v>6733238</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5881,7 +5846,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5891,12 +5856,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5923,13 +5888,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652193</t>
+          <t>https://artportalen.se/Sighting/123652186</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123652194</v>
+        <v>123652187</v>
       </c>
       <c r="B45" t="n">
         <v>99118</v>
@@ -5968,10 +5933,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>513642</v>
+        <v>513627</v>
       </c>
       <c r="R45" t="n">
-        <v>6733220</v>
+        <v>6733241</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -6003,7 +5968,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6013,7 +5978,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6045,13 +6010,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652194</t>
+          <t>https://artportalen.se/Sighting/123652187</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123652195</v>
+        <v>123652188</v>
       </c>
       <c r="B46" t="n">
         <v>99118</v>
@@ -6090,10 +6055,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513645</v>
+        <v>513629</v>
       </c>
       <c r="R46" t="n">
-        <v>6733241</v>
+        <v>6733239</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6125,7 +6090,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6135,12 +6100,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>15:36 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6167,13 +6132,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652195</t>
+          <t>https://artportalen.se/Sighting/123652188</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123652197</v>
+        <v>123652189</v>
       </c>
       <c r="B47" t="n">
         <v>99118</v>
@@ -6212,10 +6177,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513644</v>
+        <v>513629</v>
       </c>
       <c r="R47" t="n">
-        <v>6733242</v>
+        <v>6733228</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6247,7 +6212,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6257,12 +6222,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6289,13 +6254,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652197</t>
+          <t>https://artportalen.se/Sighting/123652189</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123652199</v>
+        <v>123652190</v>
       </c>
       <c r="B48" t="n">
         <v>99118</v>
@@ -6334,10 +6299,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513642</v>
+        <v>513627</v>
       </c>
       <c r="R48" t="n">
-        <v>6733246</v>
+        <v>6733227</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6369,7 +6334,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6379,12 +6344,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6411,13 +6376,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652199</t>
+          <t>https://artportalen.se/Sighting/123652190</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123652200</v>
+        <v>123652191</v>
       </c>
       <c r="B49" t="n">
         <v>99118</v>
@@ -6456,10 +6421,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513638</v>
+        <v>513628</v>
       </c>
       <c r="R49" t="n">
-        <v>6733248</v>
+        <v>6733228</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6491,7 +6456,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6501,12 +6466,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6533,13 +6498,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652200</t>
+          <t>https://artportalen.se/Sighting/123652191</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123652201</v>
+        <v>123652192</v>
       </c>
       <c r="B50" t="n">
         <v>99118</v>
@@ -6578,10 +6543,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513640</v>
+        <v>513630</v>
       </c>
       <c r="R50" t="n">
-        <v>6733246</v>
+        <v>6733221</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6613,7 +6578,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6623,12 +6588,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6655,13 +6620,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652201</t>
+          <t>https://artportalen.se/Sighting/123652192</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123652202</v>
+        <v>123652193</v>
       </c>
       <c r="B51" t="n">
         <v>99118</v>
@@ -6700,10 +6665,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513640</v>
+        <v>513631</v>
       </c>
       <c r="R51" t="n">
-        <v>6733250</v>
+        <v>6733221</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6735,7 +6700,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6745,12 +6710,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6777,13 +6742,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652202</t>
+          <t>https://artportalen.se/Sighting/123652193</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123652203</v>
+        <v>123652194</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -6822,10 +6787,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513639</v>
+        <v>513642</v>
       </c>
       <c r="R52" t="n">
-        <v>6733252</v>
+        <v>6733220</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6857,7 +6822,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6867,12 +6832,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6899,13 +6864,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652203</t>
+          <t>https://artportalen.se/Sighting/123652194</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123652204</v>
+        <v>123652195</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -6944,10 +6909,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513632</v>
+        <v>513645</v>
       </c>
       <c r="R53" t="n">
-        <v>6733247</v>
+        <v>6733241</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6979,7 +6944,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6989,12 +6954,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>15:36 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7021,13 +6986,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652204</t>
+          <t>https://artportalen.se/Sighting/123652195</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123652205</v>
+        <v>123652197</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -7066,10 +7031,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513635</v>
+        <v>513644</v>
       </c>
       <c r="R54" t="n">
-        <v>6733245</v>
+        <v>6733242</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -7101,7 +7066,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7111,7 +7076,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -7143,13 +7108,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652205</t>
+          <t>https://artportalen.se/Sighting/123652197</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123652206</v>
+        <v>123652199</v>
       </c>
       <c r="B55" t="n">
         <v>99118</v>
@@ -7188,10 +7153,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513623</v>
+        <v>513642</v>
       </c>
       <c r="R55" t="n">
-        <v>6733237</v>
+        <v>6733246</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -7223,7 +7188,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7233,7 +7198,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -7265,13 +7230,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652206</t>
+          <t>https://artportalen.se/Sighting/123652199</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123652207</v>
+        <v>123652200</v>
       </c>
       <c r="B56" t="n">
         <v>99118</v>
@@ -7310,10 +7275,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513629</v>
+        <v>513638</v>
       </c>
       <c r="R56" t="n">
-        <v>6733245</v>
+        <v>6733248</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7345,7 +7310,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7355,7 +7320,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7387,13 +7352,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652207</t>
+          <t>https://artportalen.se/Sighting/123652200</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123652208</v>
+        <v>123652201</v>
       </c>
       <c r="B57" t="n">
         <v>99118</v>
@@ -7432,10 +7397,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513626</v>
+        <v>513640</v>
       </c>
       <c r="R57" t="n">
-        <v>6733254</v>
+        <v>6733246</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7467,7 +7432,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7477,7 +7442,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -7509,13 +7474,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652208</t>
+          <t>https://artportalen.se/Sighting/123652201</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123652209</v>
+        <v>123652202</v>
       </c>
       <c r="B58" t="n">
         <v>99118</v>
@@ -7554,10 +7519,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513620</v>
+        <v>513640</v>
       </c>
       <c r="R58" t="n">
-        <v>6733253</v>
+        <v>6733250</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7589,7 +7554,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7599,7 +7564,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -7631,13 +7596,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652209</t>
+          <t>https://artportalen.se/Sighting/123652202</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123652210</v>
+        <v>123652203</v>
       </c>
       <c r="B59" t="n">
         <v>99118</v>
@@ -7676,10 +7641,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513625</v>
+        <v>513639</v>
       </c>
       <c r="R59" t="n">
-        <v>6733251</v>
+        <v>6733252</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7711,7 +7676,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7721,12 +7686,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7753,13 +7718,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652210</t>
+          <t>https://artportalen.se/Sighting/123652203</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123652211</v>
+        <v>123652204</v>
       </c>
       <c r="B60" t="n">
         <v>99118</v>
@@ -7798,10 +7763,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513625</v>
+        <v>513632</v>
       </c>
       <c r="R60" t="n">
-        <v>6733258</v>
+        <v>6733247</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7833,7 +7798,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7843,12 +7808,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7875,13 +7840,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652211</t>
+          <t>https://artportalen.se/Sighting/123652204</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123652212</v>
+        <v>123652205</v>
       </c>
       <c r="B61" t="n">
         <v>99118</v>
@@ -7920,10 +7885,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513623</v>
+        <v>513635</v>
       </c>
       <c r="R61" t="n">
-        <v>6733260</v>
+        <v>6733245</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7955,7 +7920,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7965,12 +7930,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7997,13 +7962,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652212</t>
+          <t>https://artportalen.se/Sighting/123652205</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123652213</v>
+        <v>123652206</v>
       </c>
       <c r="B62" t="n">
         <v>99118</v>
@@ -8042,10 +8007,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>513617</v>
+        <v>513623</v>
       </c>
       <c r="R62" t="n">
-        <v>6733269</v>
+        <v>6733237</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -8077,7 +8042,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8087,7 +8052,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -8119,13 +8084,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652213</t>
+          <t>https://artportalen.se/Sighting/123652206</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123652214</v>
+        <v>123652207</v>
       </c>
       <c r="B63" t="n">
         <v>99118</v>
@@ -8164,10 +8129,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>513615</v>
+        <v>513629</v>
       </c>
       <c r="R63" t="n">
-        <v>6733271</v>
+        <v>6733245</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -8199,7 +8164,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8209,12 +8174,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8241,13 +8206,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652214</t>
+          <t>https://artportalen.se/Sighting/123652207</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123652216</v>
+        <v>123652208</v>
       </c>
       <c r="B64" t="n">
         <v>99118</v>
@@ -8286,10 +8251,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>513614</v>
+        <v>513626</v>
       </c>
       <c r="R64" t="n">
-        <v>6733272</v>
+        <v>6733254</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -8321,7 +8286,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8331,12 +8296,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8363,13 +8328,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652216</t>
+          <t>https://artportalen.se/Sighting/123652208</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123652217</v>
+        <v>123652209</v>
       </c>
       <c r="B65" t="n">
         <v>99118</v>
@@ -8408,10 +8373,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>513612</v>
+        <v>513620</v>
       </c>
       <c r="R65" t="n">
-        <v>6733277</v>
+        <v>6733253</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -8443,7 +8408,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8453,12 +8418,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8485,13 +8450,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652217</t>
+          <t>https://artportalen.se/Sighting/123652209</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123652218</v>
+        <v>123652210</v>
       </c>
       <c r="B66" t="n">
         <v>99118</v>
@@ -8530,10 +8495,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>513613</v>
+        <v>513625</v>
       </c>
       <c r="R66" t="n">
-        <v>6733273</v>
+        <v>6733251</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -8565,7 +8530,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8575,12 +8540,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8607,13 +8572,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652218</t>
+          <t>https://artportalen.se/Sighting/123652210</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123652219</v>
+        <v>123652211</v>
       </c>
       <c r="B67" t="n">
         <v>99118</v>
@@ -8652,10 +8617,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>513609</v>
+        <v>513625</v>
       </c>
       <c r="R67" t="n">
-        <v>6733267</v>
+        <v>6733258</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8687,7 +8652,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8697,12 +8662,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8729,13 +8694,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652219</t>
+          <t>https://artportalen.se/Sighting/123652211</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123652220</v>
+        <v>123652212</v>
       </c>
       <c r="B68" t="n">
         <v>99118</v>
@@ -8774,10 +8739,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>513609</v>
+        <v>513623</v>
       </c>
       <c r="R68" t="n">
-        <v>6733266</v>
+        <v>6733260</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8809,7 +8774,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8819,12 +8784,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8851,13 +8816,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652220</t>
+          <t>https://artportalen.se/Sighting/123652212</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123652221</v>
+        <v>123652213</v>
       </c>
       <c r="B69" t="n">
         <v>99118</v>
@@ -8896,7 +8861,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>513613</v>
+        <v>513617</v>
       </c>
       <c r="R69" t="n">
         <v>6733269</v>
@@ -8931,7 +8896,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8941,7 +8906,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -8973,13 +8938,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652221</t>
+          <t>https://artportalen.se/Sighting/123652213</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123652222</v>
+        <v>123652214</v>
       </c>
       <c r="B70" t="n">
         <v>99118</v>
@@ -9018,10 +8983,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>513612</v>
+        <v>513615</v>
       </c>
       <c r="R70" t="n">
-        <v>6733260</v>
+        <v>6733271</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -9053,7 +9018,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9063,12 +9028,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9095,13 +9060,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652222</t>
+          <t>https://artportalen.se/Sighting/123652214</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123652223</v>
+        <v>123652216</v>
       </c>
       <c r="B71" t="n">
         <v>99118</v>
@@ -9140,10 +9105,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>513611</v>
+        <v>513614</v>
       </c>
       <c r="R71" t="n">
-        <v>6733249</v>
+        <v>6733272</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -9175,7 +9140,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9185,12 +9150,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9217,13 +9182,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652223</t>
+          <t>https://artportalen.se/Sighting/123652216</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123652224</v>
+        <v>123652217</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -9262,10 +9227,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>513610</v>
+        <v>513612</v>
       </c>
       <c r="R72" t="n">
-        <v>6733242</v>
+        <v>6733277</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -9297,7 +9262,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9307,12 +9272,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9339,13 +9304,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652224</t>
+          <t>https://artportalen.se/Sighting/123652217</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123652225</v>
+        <v>123652218</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -9384,10 +9349,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>513617</v>
+        <v>513613</v>
       </c>
       <c r="R73" t="n">
-        <v>6733234</v>
+        <v>6733273</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -9419,7 +9384,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9429,12 +9394,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9461,13 +9426,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652225</t>
+          <t>https://artportalen.se/Sighting/123652218</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123652226</v>
+        <v>123652219</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -9506,10 +9471,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>513622</v>
+        <v>513609</v>
       </c>
       <c r="R74" t="n">
-        <v>6733236</v>
+        <v>6733267</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -9541,7 +9506,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9551,12 +9516,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9583,38 +9548,38 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123652226</t>
+          <t>https://artportalen.se/Sighting/123652219</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123656499</v>
+        <v>123652220</v>
       </c>
       <c r="B75" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9628,13 +9593,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>513625</v>
+        <v>513609</v>
       </c>
       <c r="R75" t="n">
-        <v>6733311</v>
+        <v>6733266</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9663,7 +9628,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9673,7 +9638,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9700,7 +9670,968 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/123652220</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>123652221</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Bjurtjärnsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>513613</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6733269</v>
+      </c>
+      <c r="S76" t="n">
+        <v>15</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652221</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>123652222</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Bjurtjärnsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>513612</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6733260</v>
+      </c>
+      <c r="S77" t="n">
+        <v>15</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652222</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>123652223</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Bjurtjärnsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>513611</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6733249</v>
+      </c>
+      <c r="S78" t="n">
+        <v>15</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652223</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>123652224</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Bjurtjärnsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>513610</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6733242</v>
+      </c>
+      <c r="S79" t="n">
+        <v>15</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652224</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>123652225</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Bjurtjärnsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>513617</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6733234</v>
+      </c>
+      <c r="S80" t="n">
+        <v>15</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652225</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>123652226</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Bjurtjärnsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>513622</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6733236</v>
+      </c>
+      <c r="S81" t="n">
+        <v>15</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652226</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>123656499</v>
+      </c>
+      <c r="B82" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Bjurtjärnsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>513625</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6733311</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/123656499</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>136801974</v>
+      </c>
+      <c r="B83" t="n">
+        <v>98213</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>BJURTJÄRN, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>513660</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6733221</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136801974</t>
         </is>
       </c>
     </row>
@@ -9780,6 +10711,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136801971</v>
       </c>
       <c r="B2" t="n">
-        <v>93408</v>
+        <v>93410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136801973</v>
       </c>
       <c r="B3" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136801969</v>
       </c>
       <c r="B19" t="n">
-        <v>111330</v>
+        <v>111332</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>136801974</v>
       </c>
       <c r="B83" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136801971</v>
       </c>
       <c r="B2" t="n">
-        <v>93410</v>
+        <v>93412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136801973</v>
       </c>
       <c r="B3" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136801969</v>
       </c>
       <c r="B19" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>136801974</v>
       </c>
       <c r="B83" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136801971</v>
       </c>
       <c r="B2" t="n">
-        <v>93412</v>
+        <v>93414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136801973</v>
       </c>
       <c r="B3" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136801969</v>
       </c>
       <c r="B19" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>136801974</v>
       </c>
       <c r="B83" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136801971</v>
       </c>
       <c r="B2" t="n">
-        <v>93414</v>
+        <v>93415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136801973</v>
       </c>
       <c r="B3" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136801969</v>
       </c>
       <c r="B19" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>136801974</v>
       </c>
       <c r="B83" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136801971</v>
       </c>
       <c r="B2" t="n">
-        <v>93415</v>
+        <v>93421</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136801973</v>
       </c>
       <c r="B3" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136801969</v>
       </c>
       <c r="B19" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>136801974</v>
       </c>
       <c r="B83" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136801971</v>
       </c>
       <c r="B2" t="n">
-        <v>93421</v>
+        <v>93425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136801973</v>
       </c>
       <c r="B3" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136801969</v>
       </c>
       <c r="B19" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>136801974</v>
       </c>
       <c r="B83" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136801973</v>
       </c>
       <c r="B3" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136801969</v>
       </c>
       <c r="B19" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>136801974</v>
       </c>
       <c r="B83" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136801971</v>
       </c>
       <c r="B2" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136801973</v>
       </c>
       <c r="B3" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2738,7 +2738,7 @@
         <v>136801969</v>
       </c>
       <c r="B19" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -10528,7 +10528,7 @@
         <v>136801974</v>
       </c>
       <c r="B83" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136801971</v>
       </c>
       <c r="B2" t="n">
-        <v>93427</v>
+        <v>93440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136801973</v>
       </c>
       <c r="B3" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136801962</v>
       </c>
       <c r="B8" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1541,7 +1541,7 @@
         <v>136801970</v>
       </c>
       <c r="B9" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2738,7 +2738,7 @@
         <v>136801969</v>
       </c>
       <c r="B19" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -10528,7 +10528,7 @@
         <v>136801974</v>
       </c>
       <c r="B83" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136801971</v>
       </c>
       <c r="B2" t="n">
-        <v>93440</v>
+        <v>93441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136801973</v>
       </c>
       <c r="B3" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136801962</v>
       </c>
       <c r="B8" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136801970</v>
       </c>
       <c r="B9" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136801972</v>
       </c>
       <c r="B18" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136801969</v>
       </c>
       <c r="B19" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>136801974</v>
       </c>
       <c r="B83" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -1444,11 +1444,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1569,11 +1565,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136801971</v>
       </c>
       <c r="B2" t="n">
-        <v>93441</v>
+        <v>93444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136801973</v>
       </c>
       <c r="B3" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136801969</v>
       </c>
       <c r="B19" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>136801974</v>
       </c>
       <c r="B83" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136801971</v>
       </c>
       <c r="B2" t="n">
-        <v>93444</v>
+        <v>93454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136801973</v>
       </c>
       <c r="B3" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136801962</v>
       </c>
       <c r="B8" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>136801970</v>
       </c>
       <c r="B9" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>136801976</v>
       </c>
       <c r="B12" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>136801972</v>
       </c>
       <c r="B18" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136801969</v>
       </c>
       <c r="B19" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>136801974</v>
       </c>
       <c r="B83" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136801971</v>
       </c>
       <c r="B2" t="n">
-        <v>93454</v>
+        <v>93455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136801973</v>
       </c>
       <c r="B3" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136801969</v>
       </c>
       <c r="B19" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>136801974</v>
       </c>
       <c r="B83" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136801971</v>
       </c>
       <c r="B2" t="n">
-        <v>93455</v>
+        <v>93460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136801973</v>
       </c>
       <c r="B3" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136801962</v>
       </c>
       <c r="B8" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>136801970</v>
       </c>
       <c r="B9" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136801969</v>
       </c>
       <c r="B19" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>136801974</v>
       </c>
       <c r="B83" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136801971</v>
       </c>
       <c r="B2" t="n">
-        <v>93460</v>
+        <v>93462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136801973</v>
       </c>
       <c r="B3" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136801969</v>
       </c>
       <c r="B19" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>136801974</v>
       </c>
       <c r="B83" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136801971</v>
       </c>
       <c r="B2" t="n">
-        <v>93462</v>
+        <v>93468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136801973</v>
       </c>
       <c r="B3" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136801962</v>
       </c>
       <c r="B8" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>136801970</v>
       </c>
       <c r="B9" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136801969</v>
       </c>
       <c r="B19" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>136801974</v>
       </c>
       <c r="B83" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
